--- a/photographer_forms/002_league_photo_order_form--photographer_forms.xlsx
+++ b/photographer_forms/002_league_photo_order_form--photographer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email_opt_in</t>
+          <t>email_opt_in_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email Opt-in</t>
+          <t>Email Opt In 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>appointment_location</t>
+          <t>appointment_location_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Appointment Location</t>
+          <t>Appointment Location 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email_opt_in</t>
+          <t>email_opt_in_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email Opt-in</t>
+          <t>Email Opt In 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>appointment_date</t>
+          <t>appointment_date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Appointment Date</t>
+          <t>Appointment Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>appointment_location_choices</t>
+          <t>appointment_location_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>appointment_location_choices</t>
+          <t>appointment_location_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
